--- a/data/trans_dic/IQ2606_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ2606_R2-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73,22%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74,3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>65,36%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>81,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60,54%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>73,22%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,74; 75,05</t>
+          <t>55,74; 76,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,79; 88,48</t>
+          <t>63,13; 82,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,22; 80,89</t>
+          <t>51,86; 88,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,41; 77,17</t>
+          <t>53,38; 74,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,25; 82,44</t>
+          <t>71,51; 88,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,7; 89,89</t>
+          <t>35,1; 79,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,15; 73,55</t>
+          <t>58,86; 73,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,81; 83,04</t>
+          <t>70,06; 82,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,74; 81,74</t>
+          <t>53,38; 80,29</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>78,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>79,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>90,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>88,58%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>78,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,96; 86,08</t>
+          <t>70,62; 84,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,07; 94,03</t>
+          <t>85,08; 94,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,27; 97,17</t>
+          <t>71,09; 96,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,45; 85,03</t>
+          <t>73,62; 85,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,67; 94,72</t>
+          <t>84,25; 94,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,32; 96,53</t>
+          <t>68,62; 96,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,22; 83,77</t>
+          <t>74,61; 83,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,65; 93,64</t>
+          <t>86,79; 93,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,77; 94,49</t>
+          <t>76,2; 93,73</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49,13%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44,6%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71,39%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>64,61%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>41,8%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81,31%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49,13%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>44,6%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,32; 74,24</t>
+          <t>39,03; 59,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 51,61</t>
+          <t>35,45; 54,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,51; 92,72</t>
+          <t>51,24; 86,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,45; 58,72</t>
+          <t>54,9; 74,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,81; 54,88</t>
+          <t>31,11; 53,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,05; 88,55</t>
+          <t>62,59; 92,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,48; 63,76</t>
+          <t>49,86; 63,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,25; 50,82</t>
+          <t>35,71; 50,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,98; 87,58</t>
+          <t>62,28; 86,73</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>43,9%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>73,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>73,77%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>80,03%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,53; 53,94</t>
+          <t>37,22; 56,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,4; 80,67</t>
+          <t>71,76; 87,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,42; 91,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,96; 55,5</t>
+          <t>34,51; 53,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,16; 86,8</t>
+          <t>63,78; 81,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,47; 92,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,48; 52,43</t>
+          <t>38,56; 51,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,46; 81,96</t>
+          <t>70,27; 82,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,91; 95,68</t>
+          <t>61,11; 95,11</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56,06%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55,81%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>89,05%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>63,99%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>68,04%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>81,53%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56,06%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>55,81%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,11; 75,28</t>
+          <t>44,42; 68,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,67; 78,9</t>
+          <t>43,18; 67,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,89; 95,51</t>
+          <t>67,3; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,85; 68,35</t>
+          <t>51,45; 74,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,62; 68,82</t>
+          <t>55,83; 79,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,63; 100,0</t>
+          <t>58,97; 94,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,23; 68,0</t>
+          <t>51,29; 68,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,34; 69,89</t>
+          <t>52,89; 70,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,07; 94,36</t>
+          <t>72,57; 94,62</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>50,03%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84,84%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>51,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>80,76%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>80,4%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50,03%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,84%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,21; 61,57</t>
+          <t>38,23; 60,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,74; 88,18</t>
+          <t>75,38; 91,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,21; 94,25</t>
+          <t>52,29; 88,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39,51; 61,66</t>
+          <t>40,2; 62,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75,51; 91,84</t>
+          <t>71,51; 87,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,7; 88,32</t>
+          <t>50,29; 93,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,12; 58,53</t>
+          <t>43,08; 59,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76,27; 88,51</t>
+          <t>76,28; 88,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61,53; 87,18</t>
+          <t>59,49; 87,59</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47,99%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67,89%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>89,42%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>54,54%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>71,64%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47,99%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>67,89%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,6; 61,82</t>
+          <t>41,16; 54,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65,37; 78,05</t>
+          <t>60,83; 74,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,44; 97,38</t>
+          <t>76,55; 95,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,84; 55,93</t>
+          <t>47,48; 61,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,46; 74,48</t>
+          <t>65,05; 77,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,01; 96,17</t>
+          <t>77,33; 97,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,54; 56,11</t>
+          <t>45,77; 55,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>64,78; 73,79</t>
+          <t>65,23; 73,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,28; 95,5</t>
+          <t>80,23; 94,91</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>76,09%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>91,68%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>66,67%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>71,48%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>60,62%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>76,09%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>60,62; 72,86</t>
+          <t>53,89; 66,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65,69; 76,57</t>
+          <t>69,79; 81,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,04; 98,39</t>
+          <t>79,77; 96,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54,44; 66,55</t>
+          <t>60,77; 72,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,45; 81,37</t>
+          <t>65,6; 76,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,68; 96,87</t>
+          <t>77,44; 97,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,47; 67,89</t>
+          <t>59,29; 67,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>69,52; 77,26</t>
+          <t>69,71; 77,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84,28; 96,12</t>
+          <t>84,82; 96,15</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>57,57%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>73,05%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>57,57%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59,02; 65,05</t>
+          <t>54,13; 60,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>70,32; 75,94</t>
+          <t>70,58; 76,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78,18; 88,21</t>
+          <t>80,69; 89,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54,57; 60,63</t>
+          <t>58,64; 64,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>70,62; 75,96</t>
+          <t>69,98; 75,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>80,75; 89,91</t>
+          <t>77,03; 87,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,72; 62,13</t>
+          <t>57,37; 61,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>71,07; 75,01</t>
+          <t>71,28; 75,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>81,58; 87,88</t>
+          <t>80,46; 87,75</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1760,27 +1760,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41815</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13052</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>37208</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>46227</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41815</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>47200</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>20338</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30595; 42727</t>
+          <t>34588; 47393</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41418; 50349</t>
+          <t>40692; 53113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5145; 10888</t>
+          <t>9109; 15569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35006; 47885</t>
+          <t>30391; 42389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40130; 53141</t>
+          <t>40689; 50311</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11675; 18508</t>
+          <t>4340; 9787</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70376; 87508</t>
+          <t>70029; 87428</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84719; 100781</t>
+          <t>85026; 100517</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18980; 27835</t>
+          <t>15977; 24033</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82173</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>99163</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24906</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>80470</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>91984</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20343</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82173</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99163</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>48692</t>
+          <t>42497</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73451; 86658</t>
+          <t>73938; 88620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85917; 96096</t>
+          <t>92738; 102795</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16597; 22315</t>
+          <t>20556; 27808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74805; 89027</t>
+          <t>74118; 86395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93379; 103248</t>
+          <t>86108; 96184</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23504; 31372</t>
+          <t>13890; 19469</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>152419; 172048</t>
+          <t>153224; 171655</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>182997; 197761</t>
+          <t>183292; 197182</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42578; 52409</t>
+          <t>37459; 46072</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>42262</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>26168</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15133</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>30584</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>25067</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35535; 48561</t>
+          <t>26727; 40525</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19257; 32314</t>
+          <t>24312; 37411</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12007; 17257</t>
+          <t>7245; 12251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27012; 40210</t>
+          <t>35911; 48981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23874; 37631</t>
+          <t>19474; 33290</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8522; 14226</t>
+          <t>11713; 17264</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66246; 85374</t>
+          <t>66762; 85679</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47559; 66672</t>
+          <t>46851; 66395</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22533; 30369</t>
+          <t>20461; 28495</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38124</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>64972</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10578</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>32739</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>55514</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>10813</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38124</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64972</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>21851</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25754; 40225</t>
+          <t>30606; 46824</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48113; 61220</t>
+          <t>58254; 70701</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7098; 13366</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30391; 45638</t>
+          <t>25734; 39813</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56955; 70469</t>
+          <t>48402; 61564</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7225; 14057</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61904; 82208</t>
+          <t>60468; 81510</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110668; 128740</t>
+          <t>110377; 129131</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16041; 24394</t>
+          <t>15766; 24535</t>
         </is>
       </c>
     </row>
@@ -2407,27 +2407,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25830</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25443</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9834</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>28090</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>29147</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8382</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>25830</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25443</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18591</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22436; 33049</t>
+          <t>20468; 31431</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23850; 33803</t>
+          <t>19685; 30759</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6157; 9819</t>
+          <t>7432; 11044</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20205; 31492</t>
+          <t>22589; 32883</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20340; 31374</t>
+          <t>23917; 33966</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7406; 10637</t>
+          <t>6291; 10127</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46093; 61188</t>
+          <t>46154; 61861</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47172; 61802</t>
+          <t>46774; 62108</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15284; 19738</t>
+          <t>15757; 20544</t>
         </is>
       </c>
     </row>
@@ -2575,27 +2575,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>28339</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48984</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11675</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>26956</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>43305</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7138</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28339</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>48984</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>18719</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20672; 32463</t>
+          <t>21654; 34463</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37932; 47289</t>
+          <t>43523; 52813</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4724; 8367</t>
+          <t>8290; 14044</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22380; 34927</t>
+          <t>21196; 33024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43598; 53026</t>
+          <t>38350; 47111</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10056; 16236</t>
+          <t>4474; 8327</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46065; 64014</t>
+          <t>47117; 64605</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84933; 98564</t>
+          <t>84947; 98141</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16773; 23766</t>
+          <t>14725; 21681</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>65872</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>96975</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>36477</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>73242</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>97984</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>25912</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>65872</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>96975</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>60628</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>62578; 83023</t>
+          <t>56493; 75167</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>89416; 106754</t>
+          <t>86885; 106020</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22433; 27502</t>
+          <t>31229; 39089</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56055; 76772</t>
+          <t>63764; 82613</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>87782; 106389</t>
+          <t>88972; 106163</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33628; 41995</t>
+          <t>20876; 26203</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>126374; 152378</t>
+          <t>124293; 151983</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>181121; 206334</t>
+          <t>182399; 206362</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>57725; 68676</t>
+          <t>54385; 64338</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>101857</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>127274</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>36190</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>107468</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>116298</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>23357</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>101857</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>127274</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>59056</t>
+          <t>60057</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>97724; 117453</t>
+          <t>90542; 111934</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>106867; 124575</t>
+          <t>116749; 135697</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19804; 24968</t>
+          <t>31488; 38245</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91475; 111826</t>
+          <t>97955; 117513</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>117845; 136113</t>
+          <t>106720; 125050</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31534; 37865</t>
+          <t>19990; 25159</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>195774; 223516</t>
+          <t>195183; 223023</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>229381; 254943</t>
+          <t>230017; 256147</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54333; 61964</t>
+          <t>55377; 62775</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>186</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>417652</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>540595</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>428434</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>506627</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>417652</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>540595</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>114941</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>267748</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>407089; 448689</t>
+          <t>392687; 437154</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>487730; 526672</t>
+          <t>519925; 560415</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>111389; 125669</t>
+          <t>143923; 160044</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>395913; 439847</t>
+          <t>404431; 447552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>520202; 559587</t>
+          <t>485312; 524695</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>154849; 172418</t>
+          <t>107006; 121901</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>816773; 879233</t>
+          <t>811897; 874003</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1016482; 1072821</t>
+          <t>1019468; 1074166</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>272672; 293736</t>
+          <t>255275; 278403</t>
         </is>
       </c>
     </row>
